--- a/public/data/xlsx/etl2.xlsx
+++ b/public/data/xlsx/etl2.xlsx
@@ -421,6 +421,11 @@
   </sheetPr>
   <dimension ref="A1:C598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -10601,6 +10606,21 @@
   </sheetPr>
   <dimension ref="A1:N599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="D1" s="1" t="inlineStr">
